--- a/data/trans_dic/Q23_tabaco_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,33; 50,44</t>
+          <t>42,18; 50,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,02; 49,58</t>
+          <t>42,03; 49,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,95; 50,59</t>
+          <t>40,82; 50,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,35; 59,02</t>
+          <t>48,46; 59,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,79; 32,09</t>
+          <t>20,15; 31,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,41; 37,4</t>
+          <t>25,05; 36,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,22; 41,11</t>
+          <t>26,28; 40,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,33; 34,5</t>
+          <t>21,22; 33,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,88; 44,63</t>
+          <t>37,79; 44,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,0; 45,41</t>
+          <t>38,74; 45,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,27; 46,11</t>
+          <t>37,96; 46,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,17; 50,7</t>
+          <t>41,82; 50,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,4; 35,77</t>
+          <t>29,32; 35,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,45; 36,32</t>
+          <t>30,21; 36,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,02; 38,14</t>
+          <t>32,39; 38,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 32,41</t>
+          <t>13,23; 32,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,49; 32,95</t>
+          <t>25,57; 32,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,97; 32,42</t>
+          <t>25,67; 32,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,56; 28,29</t>
+          <t>22,31; 28,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,41; 27,66</t>
+          <t>21,66; 27,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,2</t>
+          <t>28,67; 33,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,25; 33,51</t>
+          <t>29,31; 33,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,8; 32,85</t>
+          <t>28,86; 33,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,05; 29,09</t>
+          <t>15,01; 29,36</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 25,22</t>
+          <t>14,4; 24,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,7; 26,15</t>
+          <t>14,56; 25,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,89; 30,88</t>
+          <t>18,26; 31,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,49; 25,15</t>
+          <t>15,0; 25,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,92; 22,74</t>
+          <t>11,13; 23,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,85; 25,07</t>
+          <t>13,37; 25,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,72; 28,91</t>
+          <t>17,12; 28,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 26,98</t>
+          <t>16,77; 26,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 22,27</t>
+          <t>14,47; 21,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,6; 23,67</t>
+          <t>15,37; 23,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 27,69</t>
+          <t>19,27; 28,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,75; 24,38</t>
+          <t>17,11; 24,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,03; 37,64</t>
+          <t>33,25; 37,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,56; 38,1</t>
+          <t>33,71; 38,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,77; 38,44</t>
+          <t>33,81; 38,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 35,03</t>
+          <t>17,65; 35,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,71; 29,28</t>
+          <t>23,53; 29,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,13; 30,47</t>
+          <t>25,15; 30,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,55; 28,55</t>
+          <t>23,4; 28,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,84; 26,6</t>
+          <t>21,62; 26,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,04; 33,72</t>
+          <t>30,17; 33,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,96; 34,24</t>
+          <t>30,84; 34,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,97; 33,66</t>
+          <t>30,14; 33,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 30,87</t>
+          <t>20,83; 30,71</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>249859; 297769</t>
+          <t>248971; 297815</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>285145; 336453</t>
+          <t>285226; 337708</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175173; 216402</t>
+          <t>174610; 214334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>145477; 177608</t>
+          <t>145810; 178798</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41474; 67269</t>
+          <t>42232; 66489</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66895; 98472</t>
+          <t>65947; 97263</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45366; 71132</t>
+          <t>45472; 70711</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24988; 40416</t>
+          <t>24856; 39801</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>302978; 356968</t>
+          <t>302280; 357205</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>367328; 427695</t>
+          <t>364873; 427402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>229916; 277018</t>
+          <t>228065; 278014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>176280; 211955</t>
+          <t>174818; 212180</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>263504; 320553</t>
+          <t>262783; 317743</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>341163; 406944</t>
+          <t>338514; 404797</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>354283; 421990</t>
+          <t>358427; 423288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148549; 365816</t>
+          <t>149402; 366988</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>157934; 204144</t>
+          <t>158446; 204070</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>220253; 274932</t>
+          <t>217665; 273959</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>191457; 240068</t>
+          <t>189284; 240951</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>141122; 182347</t>
+          <t>142819; 183656</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>432968; 503240</t>
+          <t>434643; 503535</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>575785; 659702</t>
+          <t>577024; 663687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>563040; 642162</t>
+          <t>564159; 646084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>269085; 520168</t>
+          <t>268333; 524979</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33664; 59164</t>
+          <t>33785; 57955</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35495; 63162</t>
+          <t>35174; 61674</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39494; 68159</t>
+          <t>40307; 68544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36724; 59634</t>
+          <t>35583; 60260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18469; 38456</t>
+          <t>18821; 39077</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26495; 51683</t>
+          <t>27551; 53276</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36192; 62588</t>
+          <t>37078; 62722</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31639; 52136</t>
+          <t>32408; 52094</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57053; 89884</t>
+          <t>58398; 88769</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69835; 105956</t>
+          <t>68799; 104742</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84483; 121087</t>
+          <t>84261; 122666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72084; 104902</t>
+          <t>73657; 105901</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>568525; 647867</t>
+          <t>572225; 650850</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>684862; 777515</t>
+          <t>688022; 782753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>592734; 674617</t>
+          <t>593427; 674271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>298395; 583959</t>
+          <t>294204; 587316</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>236687; 292305</t>
+          <t>234941; 292311</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>331091; 401390</t>
+          <t>331337; 402629</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>291594; 353450</t>
+          <t>289723; 353981</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>211774; 257936</t>
+          <t>209671; 258198</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>816937; 916984</t>
+          <t>820550; 919160</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1039640; 1149899</t>
+          <t>1035795; 1151495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>897120; 1007602</t>
+          <t>902029; 1011252</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>515318; 813850</t>
+          <t>549260; 809727</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q23_tabaco_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,51%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,18; 50,45</t>
+          <t>42,61; 50,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,03; 49,76</t>
+          <t>42,24; 49,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,82; 50,11</t>
+          <t>40,78; 50,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,46; 59,42</t>
+          <t>47,23; 58,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,15; 31,72</t>
+          <t>20,25; 32,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,05; 36,94</t>
+          <t>24,93; 36,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,28; 40,86</t>
+          <t>26,01; 41,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 33,97</t>
+          <t>20,88; 34,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,79; 44,66</t>
+          <t>37,81; 44,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,74; 45,37</t>
+          <t>38,27; 45,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,96; 46,28</t>
+          <t>37,8; 45,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,82; 50,75</t>
+          <t>41,27; 49,98</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,32; 35,45</t>
+          <t>29,11; 35,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 36,13</t>
+          <t>30,26; 36,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,39; 38,25</t>
+          <t>32,44; 38,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,23; 32,51</t>
+          <t>27,39; 34,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,57; 32,93</t>
+          <t>25,92; 33,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,67; 32,31</t>
+          <t>25,52; 32,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,31; 28,4</t>
+          <t>22,5; 28,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 27,86</t>
+          <t>21,07; 26,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,67; 33,22</t>
+          <t>28,8; 33,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,31; 33,71</t>
+          <t>29,19; 33,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,86; 33,05</t>
+          <t>28,62; 32,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,01; 29,36</t>
+          <t>25,55; 29,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,4; 24,71</t>
+          <t>14,0; 25,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 25,54</t>
+          <t>14,73; 25,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 31,05</t>
+          <t>18,11; 30,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 25,41</t>
+          <t>15,43; 25,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 23,11</t>
+          <t>11,08; 23,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,37; 25,84</t>
+          <t>13,59; 25,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,12; 28,97</t>
+          <t>17,1; 29,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 26,96</t>
+          <t>16,28; 25,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 21,99</t>
+          <t>14,4; 22,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,37; 23,4</t>
+          <t>15,69; 24,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,27; 28,05</t>
+          <t>19,6; 28,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 24,61</t>
+          <t>16,82; 24,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,25; 37,82</t>
+          <t>32,97; 37,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,71; 38,36</t>
+          <t>33,7; 38,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,81; 38,42</t>
+          <t>33,96; 38,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,65; 35,23</t>
+          <t>31,12; 36,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,28</t>
+          <t>23,52; 29,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 30,56</t>
+          <t>25,16; 30,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,4; 28,59</t>
+          <t>23,38; 28,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,62; 26,63</t>
+          <t>21,31; 26,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,17; 33,8</t>
+          <t>30,22; 33,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 34,29</t>
+          <t>30,95; 34,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,14; 33,79</t>
+          <t>30,26; 33,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,83; 30,71</t>
+          <t>27,69; 31,3</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161593</t>
+          <t>170168</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>193643</t>
+          <t>204354</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>248971; 297815</t>
+          <t>251498; 300354</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>285226; 337708</t>
+          <t>286662; 337176</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>174610; 214334</t>
+          <t>174428; 215036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>145810; 178798</t>
+          <t>152241; 187254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42232; 66489</t>
+          <t>42455; 69010</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65947; 97263</t>
+          <t>65631; 97200</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45472; 70711</t>
+          <t>45008; 71471</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24856; 39801</t>
+          <t>26450; 43387</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>302280; 357205</t>
+          <t>302439; 357205</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>364873; 427402</t>
+          <t>360504; 424188</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>228065; 278014</t>
+          <t>227110; 276107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>174818; 212180</t>
+          <t>185308; 224408</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>277869</t>
+          <t>297329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>169881</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>439688</t>
+          <t>467210</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>262783; 317743</t>
+          <t>260929; 316760</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>338514; 404797</t>
+          <t>339079; 405423</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>358427; 423288</t>
+          <t>358998; 422265</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149402; 366988</t>
+          <t>264567; 331320</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>158446; 204070</t>
+          <t>160613; 205518</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>217665; 273959</t>
+          <t>216377; 273543</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>189284; 240951</t>
+          <t>190918; 239787</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>142819; 183656</t>
+          <t>150769; 191658</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>434643; 503535</t>
+          <t>436596; 505075</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>577024; 663687</t>
+          <t>574698; 662419</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>564159; 646084</t>
+          <t>559614; 642457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>268333; 524979</t>
+          <t>429765; 503118</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>50840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88442</t>
+          <t>93912</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33785; 57955</t>
+          <t>32849; 59081</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35174; 61674</t>
+          <t>35568; 61265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40307; 68544</t>
+          <t>39981; 68325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35583; 60260</t>
+          <t>39259; 64155</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18821; 39077</t>
+          <t>18736; 39306</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27551; 53276</t>
+          <t>28016; 52385</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37078; 62722</t>
+          <t>37027; 63487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32408; 52094</t>
+          <t>34342; 53723</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58398; 88769</t>
+          <t>58110; 90310</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68799; 104742</t>
+          <t>70242; 109267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84261; 122666</t>
+          <t>85697; 122718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73657; 105901</t>
+          <t>78315; 112256</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>487349</t>
+          <t>518337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>234424</t>
+          <t>247139</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>721773</t>
+          <t>765476</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>572225; 650850</t>
+          <t>567441; 653171</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>688022; 782753</t>
+          <t>687633; 776008</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>593427; 674271</t>
+          <t>596034; 677659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>294204; 587316</t>
+          <t>480198; 556779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>234941; 292311</t>
+          <t>234847; 290074</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>331337; 402629</t>
+          <t>331478; 400047</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>289723; 353981</t>
+          <t>289412; 350416</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>209671; 258198</t>
+          <t>224465; 275724</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>820550; 919160</t>
+          <t>821881; 921289</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1035795; 1151495</t>
+          <t>1039296; 1151292</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>902029; 1011252</t>
+          <t>905658; 1013617</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>549260; 809727</t>
+          <t>718829; 812747</t>
         </is>
       </c>
     </row>
